--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/150.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/150.xlsx
@@ -426,13 +426,13 @@
         <v>-6.803564486455899</v>
       </c>
       <c r="E2">
-        <v>-20.70678052044365</v>
+        <v>-21.32771053277347</v>
       </c>
       <c r="F2">
-        <v>-1.171090480709461</v>
+        <v>-2.259363126341729</v>
       </c>
       <c r="G2">
-        <v>-11.1000944016335</v>
+        <v>-11.71845186878327</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.887461118198851</v>
       </c>
       <c r="E3">
-        <v>-22.77105945164583</v>
+        <v>-21.62550824439765</v>
       </c>
       <c r="F3">
-        <v>-1.414532749778985</v>
+        <v>-1.915274217832064</v>
       </c>
       <c r="G3">
-        <v>-11.45086360191712</v>
+        <v>-11.94167444744035</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.998074585838708</v>
       </c>
       <c r="E4">
-        <v>-22.51645098458854</v>
+        <v>-21.86989150517321</v>
       </c>
       <c r="F4">
-        <v>-0.9881480249033988</v>
+        <v>-1.967431542981932</v>
       </c>
       <c r="G4">
-        <v>-11.41943806927389</v>
+        <v>-11.30735488786051</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.115868488575858</v>
       </c>
       <c r="E5">
-        <v>-22.48847079989317</v>
+        <v>-22.93427235028894</v>
       </c>
       <c r="F5">
-        <v>-1.229008272778397</v>
+        <v>-1.877157720159648</v>
       </c>
       <c r="G5">
-        <v>-11.37315609453493</v>
+        <v>-11.40707097214578</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.240649656881757</v>
       </c>
       <c r="E6">
-        <v>-24.74016754533957</v>
+        <v>-23.44331900273921</v>
       </c>
       <c r="F6">
-        <v>-1.219709848681973</v>
+        <v>-1.840628374430995</v>
       </c>
       <c r="G6">
-        <v>-11.33285011416502</v>
+        <v>-11.30366068426408</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.371184704951941</v>
       </c>
       <c r="E7">
-        <v>-24.08840824534555</v>
+        <v>-23.63162975741826</v>
       </c>
       <c r="F7">
-        <v>-1.459509786281388</v>
+        <v>-1.956388577135212</v>
       </c>
       <c r="G7">
-        <v>-10.92634412760573</v>
+        <v>-11.18386144721167</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.492605324384408</v>
       </c>
       <c r="E8">
-        <v>-25.21007848747596</v>
+        <v>-24.2396349761052</v>
       </c>
       <c r="F8">
-        <v>-0.9910448257109887</v>
+        <v>-1.853283343243563</v>
       </c>
       <c r="G8">
-        <v>-12.35934789398813</v>
+        <v>-10.88005693137759</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.602379042770253</v>
       </c>
       <c r="E9">
-        <v>-25.51169715351899</v>
+        <v>-24.40559730064535</v>
       </c>
       <c r="F9">
-        <v>-1.347162457276704</v>
+        <v>-1.663946719455291</v>
       </c>
       <c r="G9">
-        <v>-10.52521235878724</v>
+        <v>-10.45664637359083</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.684352069463852</v>
       </c>
       <c r="E10">
-        <v>-26.12981959499322</v>
+        <v>-25.20261516672525</v>
       </c>
       <c r="F10">
-        <v>-1.618281309641163</v>
+        <v>-1.53423349621832</v>
       </c>
       <c r="G10">
-        <v>-11.22969698462555</v>
+        <v>-10.40721845161958</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.722669301813703</v>
       </c>
       <c r="E11">
-        <v>-24.5746703804678</v>
+        <v>-26.41621258831942</v>
       </c>
       <c r="F11">
-        <v>-0.928908158459595</v>
+        <v>-1.418633996790246</v>
       </c>
       <c r="G11">
-        <v>-9.942438035042048</v>
+        <v>-10.1181920555435</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.711163457022215</v>
       </c>
       <c r="E12">
-        <v>-26.08351959514403</v>
+        <v>-26.59141165484599</v>
       </c>
       <c r="F12">
-        <v>-0.7133769006599971</v>
+        <v>-1.290708390408515</v>
       </c>
       <c r="G12">
-        <v>-9.704808062358916</v>
+        <v>-9.820232996848922</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.634995169431194</v>
       </c>
       <c r="E13">
-        <v>-27.89689472379067</v>
+        <v>-27.84684852732649</v>
       </c>
       <c r="F13">
-        <v>-0.0793502891290752</v>
+        <v>-1.409655322511302</v>
       </c>
       <c r="G13">
-        <v>-10.49294747175797</v>
+        <v>-9.473173664629277</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.504913343114731</v>
       </c>
       <c r="E14">
-        <v>-27.93003319695148</v>
+        <v>-27.56249060754945</v>
       </c>
       <c r="F14">
-        <v>-0.2904033927491388</v>
+        <v>-1.07672535128475</v>
       </c>
       <c r="G14">
-        <v>-9.074640892051242</v>
+        <v>-9.075651250208004</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.330188409499741</v>
       </c>
       <c r="E15">
-        <v>-29.41794607333925</v>
+        <v>-28.85203157482378</v>
       </c>
       <c r="F15">
-        <v>-0.4782912019499143</v>
+        <v>-0.8683594715193679</v>
       </c>
       <c r="G15">
-        <v>-9.740111856092247</v>
+        <v>-8.919150165693718</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.127227928273117</v>
       </c>
       <c r="E16">
-        <v>-29.45634043543163</v>
+        <v>-29.31842267036238</v>
       </c>
       <c r="F16">
-        <v>0.2169708130981556</v>
+        <v>-0.7330572534157078</v>
       </c>
       <c r="G16">
-        <v>-9.68491549394693</v>
+        <v>-8.421534414393752</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.923899571595983</v>
       </c>
       <c r="E17">
-        <v>-29.24435014638407</v>
+        <v>-29.39706788000934</v>
       </c>
       <c r="F17">
-        <v>-0.2420739533676073</v>
+        <v>-0.5872803295036481</v>
       </c>
       <c r="G17">
-        <v>-8.106430595969334</v>
+        <v>-8.138147226634475</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.731996032889267</v>
       </c>
       <c r="E18">
-        <v>-31.23963800766386</v>
+        <v>-30.63509033740483</v>
       </c>
       <c r="F18">
-        <v>-0.6138145941501219</v>
+        <v>-0.3864467945319219</v>
       </c>
       <c r="G18">
-        <v>-8.152625110764493</v>
+        <v>-8.044343173475774</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.576785860324061</v>
       </c>
       <c r="E19">
-        <v>-32.00164845548677</v>
+        <v>-31.08091680706855</v>
       </c>
       <c r="F19">
-        <v>0.5830122861494095</v>
+        <v>-0.2730010503511268</v>
       </c>
       <c r="G19">
-        <v>-7.381680065242513</v>
+        <v>-7.698287672551412</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.469707924636829</v>
       </c>
       <c r="E20">
-        <v>-32.38970998543912</v>
+        <v>-31.64026300187381</v>
       </c>
       <c r="F20">
-        <v>0.6227573541357297</v>
+        <v>0.1161046562962738</v>
       </c>
       <c r="G20">
-        <v>-7.21622934826989</v>
+        <v>-7.014557160840162</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.414819614484202</v>
       </c>
       <c r="E21">
-        <v>-31.85880913499761</v>
+        <v>-32.91096500257871</v>
       </c>
       <c r="F21">
-        <v>0.8050810194919009</v>
+        <v>0.02584243061762842</v>
       </c>
       <c r="G21">
-        <v>-7.537400537124056</v>
+        <v>-7.407547322651263</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.4207821999366</v>
       </c>
       <c r="E22">
-        <v>-32.99312382900647</v>
+        <v>-32.45351161781113</v>
       </c>
       <c r="F22">
-        <v>1.363051077934786</v>
+        <v>0.1832322371495345</v>
       </c>
       <c r="G22">
-        <v>-6.637993803996347</v>
+        <v>-7.059190450369835</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.474043043722328</v>
       </c>
       <c r="E23">
-        <v>-32.79286013213456</v>
+        <v>-33.17509262999251</v>
       </c>
       <c r="F23">
-        <v>1.515255304525168</v>
+        <v>0.4693958982836377</v>
       </c>
       <c r="G23">
-        <v>-7.737196904565069</v>
+        <v>-7.026801552972484</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.571497358196961</v>
       </c>
       <c r="E24">
-        <v>-33.31402793183634</v>
+        <v>-33.48187581431795</v>
       </c>
       <c r="F24">
-        <v>1.465241794213745</v>
+        <v>0.5290557470006609</v>
       </c>
       <c r="G24">
-        <v>-7.066636293943691</v>
+        <v>-6.795400816883749</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.698874038150837</v>
       </c>
       <c r="E25">
-        <v>-36.27862132458388</v>
+        <v>-33.59670172442115</v>
       </c>
       <c r="F25">
-        <v>1.283801168508958</v>
+        <v>0.6292500978388723</v>
       </c>
       <c r="G25">
-        <v>-7.516809594533945</v>
+        <v>-6.973952250214578</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.836939631924271</v>
       </c>
       <c r="E26">
-        <v>-34.04181176513134</v>
+        <v>-33.57399404150265</v>
       </c>
       <c r="F26">
-        <v>0.8672334257239479</v>
+        <v>0.5131461226624936</v>
       </c>
       <c r="G26">
-        <v>-7.769422630425476</v>
+        <v>-6.850035868941976</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.979192348987817</v>
       </c>
       <c r="E27">
-        <v>-34.11107902360683</v>
+        <v>-33.85481965504792</v>
       </c>
       <c r="F27">
-        <v>1.280835613206935</v>
+        <v>0.7719943686892831</v>
       </c>
       <c r="G27">
-        <v>-8.800190283027346</v>
+        <v>-7.062292014944078</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.105251629080165</v>
       </c>
       <c r="E28">
-        <v>-34.02350648621716</v>
+        <v>-33.88444658803358</v>
       </c>
       <c r="F28">
-        <v>1.564524940908877</v>
+        <v>0.4536444921194051</v>
       </c>
       <c r="G28">
-        <v>-7.664663892962464</v>
+        <v>-7.064840101665005</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.209251340312806</v>
       </c>
       <c r="E29">
-        <v>-34.77792278713262</v>
+        <v>-34.18164831383265</v>
       </c>
       <c r="F29">
-        <v>1.251163492838657</v>
+        <v>0.6900721460220232</v>
       </c>
       <c r="G29">
-        <v>-7.232789301211322</v>
+        <v>-7.281868688779661</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.282204262376778</v>
       </c>
       <c r="E30">
-        <v>-33.80417954936429</v>
+        <v>-33.74589130502598</v>
       </c>
       <c r="F30">
-        <v>1.270928339069453</v>
+        <v>0.7109428627355567</v>
       </c>
       <c r="G30">
-        <v>-7.557357068778526</v>
+        <v>-7.577496352554373</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.312800718450791</v>
       </c>
       <c r="E31">
-        <v>-35.67066802103849</v>
+        <v>-33.58913457338731</v>
       </c>
       <c r="F31">
-        <v>1.006352760819708</v>
+        <v>0.3021278104733475</v>
       </c>
       <c r="G31">
-        <v>-8.303860323438503</v>
+        <v>-7.465855692349187</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.303351166070791</v>
       </c>
       <c r="E32">
-        <v>-33.34232583719805</v>
+        <v>-33.54426327823386</v>
       </c>
       <c r="F32">
-        <v>1.233645179004253</v>
+        <v>0.6141854082515605</v>
       </c>
       <c r="G32">
-        <v>-7.697718530230549</v>
+        <v>-7.43851858573564</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.245017340949699</v>
       </c>
       <c r="E33">
-        <v>-33.90945099681471</v>
+        <v>-33.25013285220951</v>
       </c>
       <c r="F33">
-        <v>1.60982504069837</v>
+        <v>0.4370589199805534</v>
       </c>
       <c r="G33">
-        <v>-7.837172757937161</v>
+        <v>-7.418635154929722</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.141363817350746</v>
       </c>
       <c r="E34">
-        <v>-34.1319759063877</v>
+        <v>-32.76718082651315</v>
       </c>
       <c r="F34">
-        <v>1.71160488674554</v>
+        <v>0.6096790895803312</v>
       </c>
       <c r="G34">
-        <v>-7.498986041210415</v>
+        <v>-7.652355537587661</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.994296069325012</v>
       </c>
       <c r="E35">
-        <v>-32.45020566159657</v>
+        <v>-32.5028351555048</v>
       </c>
       <c r="F35">
-        <v>0.8781711889105125</v>
+        <v>0.5905230933905926</v>
       </c>
       <c r="G35">
-        <v>-6.731763917475362</v>
+        <v>-7.578796503360748</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.802916472323833</v>
       </c>
       <c r="E36">
-        <v>-33.41935752424531</v>
+        <v>-31.53295648087421</v>
       </c>
       <c r="F36">
-        <v>1.357129907739576</v>
+        <v>0.4020090384333007</v>
       </c>
       <c r="G36">
-        <v>-7.798954067867854</v>
+        <v>-7.456678925111424</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.579787103844375</v>
       </c>
       <c r="E37">
-        <v>-30.38927006551088</v>
+        <v>-31.80982200742126</v>
       </c>
       <c r="F37">
-        <v>0.4623887384233567</v>
+        <v>0.6389999821698225</v>
       </c>
       <c r="G37">
-        <v>-7.560612667283644</v>
+        <v>-7.381818434705842</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.326201913118525</v>
       </c>
       <c r="E38">
-        <v>-31.27708543757418</v>
+        <v>-31.40102972314103</v>
       </c>
       <c r="F38">
-        <v>0.895204079446876</v>
+        <v>0.5833742827044329</v>
       </c>
       <c r="G38">
-        <v>-7.523688906531529</v>
+        <v>-7.60593519338537</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.054631226582222</v>
       </c>
       <c r="E39">
-        <v>-31.37203615488241</v>
+        <v>-30.32234521822259</v>
       </c>
       <c r="F39">
-        <v>0.2018870710605793</v>
+        <v>0.4116868548002073</v>
       </c>
       <c r="G39">
-        <v>-7.847169298976533</v>
+        <v>-7.300569452285806</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.775127087724911</v>
       </c>
       <c r="E40">
-        <v>-30.06221298010328</v>
+        <v>-30.5331559952539</v>
       </c>
       <c r="F40">
-        <v>0.4489625595587823</v>
+        <v>0.5335844315917658</v>
       </c>
       <c r="G40">
-        <v>-8.015011457994616</v>
+        <v>-7.184845587540118</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.491507534822739</v>
       </c>
       <c r="E41">
-        <v>-31.86343581241347</v>
+        <v>-29.91847033615096</v>
       </c>
       <c r="F41">
-        <v>0.7324232578575507</v>
+        <v>0.410200763679585</v>
       </c>
       <c r="G41">
-        <v>-6.948554926832228</v>
+        <v>-7.312051506997522</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.218443851127218</v>
       </c>
       <c r="E42">
-        <v>-29.69723292208867</v>
+        <v>-29.71925740174424</v>
       </c>
       <c r="F42">
-        <v>0.7231289755981403</v>
+        <v>0.3406195585792322</v>
       </c>
       <c r="G42">
-        <v>-7.581378529761359</v>
+        <v>-7.540000838736804</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.957222193901468</v>
       </c>
       <c r="E43">
-        <v>-31.40745058784922</v>
+        <v>-28.63469610280116</v>
       </c>
       <c r="F43">
-        <v>1.272858435117976</v>
+        <v>0.4760269793430477</v>
       </c>
       <c r="G43">
-        <v>-7.617769698616887</v>
+        <v>-7.609488416773876</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.717610910451399</v>
       </c>
       <c r="E44">
-        <v>-30.62465331734553</v>
+        <v>-28.90566822247828</v>
       </c>
       <c r="F44">
-        <v>1.034692866404285</v>
+        <v>0.509521186907843</v>
       </c>
       <c r="G44">
-        <v>-7.299392006475213</v>
+        <v>-7.37944526787252</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.506733866054368</v>
       </c>
       <c r="E45">
-        <v>-29.92146687812183</v>
+        <v>-28.36671429527793</v>
       </c>
       <c r="F45">
-        <v>0.392091823886985</v>
+        <v>0.4593370329114433</v>
       </c>
       <c r="G45">
-        <v>-7.115942816291456</v>
+        <v>-7.65521430291493</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.323096991834297</v>
       </c>
       <c r="E46">
-        <v>-28.32736261797518</v>
+        <v>-28.27364498269984</v>
       </c>
       <c r="F46">
-        <v>0.9772737515118342</v>
+        <v>0.3930204237455233</v>
       </c>
       <c r="G46">
-        <v>-7.200379517857241</v>
+        <v>-7.493910753725291</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.176752941830626</v>
       </c>
       <c r="E47">
-        <v>-27.02597461539677</v>
+        <v>-27.83380744376652</v>
       </c>
       <c r="F47">
-        <v>0.8687808160323773</v>
+        <v>0.7139490080403161</v>
       </c>
       <c r="G47">
-        <v>-6.633069939697507</v>
+        <v>-7.383695560066852</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.064014614832663</v>
       </c>
       <c r="E48">
-        <v>-28.18620119486124</v>
+        <v>-27.22684883433343</v>
       </c>
       <c r="F48">
-        <v>0.7444760035682836</v>
+        <v>0.4707138308214917</v>
       </c>
       <c r="G48">
-        <v>-7.286526257130207</v>
+        <v>-7.127529300786817</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.986621498485949</v>
       </c>
       <c r="E49">
-        <v>-25.89449033490579</v>
+        <v>-26.52120992382241</v>
       </c>
       <c r="F49">
-        <v>1.010024085148916</v>
+        <v>0.5485232093338521</v>
       </c>
       <c r="G49">
-        <v>-6.306006300301199</v>
+        <v>-7.268023910212987</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.946110928530447</v>
       </c>
       <c r="E50">
-        <v>-26.41578065434164</v>
+        <v>-26.17573749940053</v>
       </c>
       <c r="F50">
-        <v>0.1528767136739466</v>
+        <v>0.6343810055318124</v>
       </c>
       <c r="G50">
-        <v>-7.06872227887199</v>
+        <v>-7.689112210685944</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.934857031053223</v>
       </c>
       <c r="E51">
-        <v>-26.59819384893943</v>
+        <v>-25.75482614447445</v>
       </c>
       <c r="F51">
-        <v>0.7842956246208558</v>
+        <v>0.4474035721067136</v>
       </c>
       <c r="G51">
-        <v>-6.778389205128055</v>
+        <v>-7.67861962817426</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.956285741872587</v>
       </c>
       <c r="E52">
-        <v>-25.19955840319017</v>
+        <v>-25.5646589043332</v>
       </c>
       <c r="F52">
-        <v>0.6012960114640001</v>
+        <v>0.5186415120126655</v>
       </c>
       <c r="G52">
-        <v>-6.819101156281875</v>
+        <v>-7.513094504980791</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.002066499943962</v>
       </c>
       <c r="E53">
-        <v>-24.42897988040414</v>
+        <v>-24.64151216352959</v>
       </c>
       <c r="F53">
-        <v>0.9258520166156521</v>
+        <v>0.5144557715263196</v>
       </c>
       <c r="G53">
-        <v>-6.541913181554196</v>
+        <v>-7.577660829463614</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.066691910528717</v>
       </c>
       <c r="E54">
-        <v>-24.15323987412612</v>
+        <v>-24.61741523142293</v>
       </c>
       <c r="F54">
-        <v>0.9244669863181713</v>
+        <v>0.3948569142775298</v>
       </c>
       <c r="G54">
-        <v>-7.602582997330381</v>
+        <v>-7.848622178341488</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.147177771575014</v>
       </c>
       <c r="E55">
-        <v>-25.80142932875035</v>
+        <v>-24.16828280554465</v>
       </c>
       <c r="F55">
-        <v>0.6619333337163268</v>
+        <v>0.4072915373609532</v>
       </c>
       <c r="G55">
-        <v>-7.276200762272354</v>
+        <v>-7.919331584847201</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.232099647444053</v>
       </c>
       <c r="E56">
-        <v>-24.12412586273907</v>
+        <v>-23.63565006598069</v>
       </c>
       <c r="F56">
-        <v>0.9704016155382095</v>
+        <v>0.3360279180655145</v>
       </c>
       <c r="G56">
-        <v>-7.144666228282884</v>
+        <v>-8.076269969080498</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.321342561591687</v>
       </c>
       <c r="E57">
-        <v>-22.7482043297253</v>
+        <v>-23.15776080488929</v>
       </c>
       <c r="F57">
-        <v>0.1100227828249198</v>
+        <v>0.2073211612229441</v>
       </c>
       <c r="G57">
-        <v>-7.180663174705154</v>
+        <v>-8.464391092229173</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.406691636064766</v>
       </c>
       <c r="E58">
-        <v>-24.54884155923869</v>
+        <v>-23.26199394950851</v>
       </c>
       <c r="F58">
-        <v>0.3893606965599551</v>
+        <v>0.4241264480880475</v>
       </c>
       <c r="G58">
-        <v>-6.979011873232155</v>
+        <v>-8.233662622872648</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.481873844085837</v>
       </c>
       <c r="E59">
-        <v>-23.80401294666659</v>
+        <v>-22.81156156848556</v>
       </c>
       <c r="F59">
-        <v>0.6353468819234767</v>
+        <v>0.4067315609966607</v>
       </c>
       <c r="G59">
-        <v>-9.080821829870704</v>
+        <v>-8.342721256677224</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.545257455821961</v>
       </c>
       <c r="E60">
-        <v>-23.63199108680352</v>
+        <v>-22.46702776982308</v>
       </c>
       <c r="F60">
-        <v>0.6503071972180358</v>
+        <v>0.3202632580228371</v>
       </c>
       <c r="G60">
-        <v>-7.568805183810557</v>
+        <v>-8.339947340549166</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.587766469763726</v>
       </c>
       <c r="E61">
-        <v>-23.7504531334216</v>
+        <v>-22.5694708803613</v>
       </c>
       <c r="F61">
-        <v>0.9043475988389769</v>
+        <v>0.1397644860550332</v>
       </c>
       <c r="G61">
-        <v>-8.29286778333762</v>
+        <v>-8.276844338409663</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.611035715799539</v>
       </c>
       <c r="E62">
-        <v>-24.60671655905017</v>
+        <v>-22.21941331063681</v>
       </c>
       <c r="F62">
-        <v>0.3946639046726775</v>
+        <v>0.1323721353524504</v>
       </c>
       <c r="G62">
-        <v>-8.203537241035793</v>
+        <v>-9.005003196200184</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.610765923705946</v>
       </c>
       <c r="E63">
-        <v>-22.1306882571045</v>
+        <v>-21.80568285809136</v>
       </c>
       <c r="F63">
-        <v>0.04136189390907716</v>
+        <v>0.008395356379865238</v>
       </c>
       <c r="G63">
-        <v>-8.740468195133333</v>
+        <v>-8.781543039785319</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.584793462060084</v>
       </c>
       <c r="E64">
-        <v>-23.65872115489011</v>
+        <v>-21.36948353227859</v>
       </c>
       <c r="F64">
-        <v>0.5479599194999484</v>
+        <v>0.03302934620431693</v>
       </c>
       <c r="G64">
-        <v>-9.076497131455524</v>
+        <v>-9.333702467082823</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.535436939441238</v>
       </c>
       <c r="E65">
-        <v>-22.73716509402391</v>
+        <v>-21.52674487909323</v>
       </c>
       <c r="F65">
-        <v>0.2796964495729397</v>
+        <v>-0.1232106863725034</v>
       </c>
       <c r="G65">
-        <v>-8.492904339281017</v>
+        <v>-9.30255106262166</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.457463841141348</v>
       </c>
       <c r="E66">
-        <v>-23.33740380753343</v>
+        <v>-21.69382857069108</v>
       </c>
       <c r="F66">
-        <v>-0.004985262277555177</v>
+        <v>-0.2407005202137657</v>
       </c>
       <c r="G66">
-        <v>-7.963220812168406</v>
+        <v>-9.378581166604061</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.354337807995045</v>
       </c>
       <c r="E67">
-        <v>-23.11795227434081</v>
+        <v>-21.28010642456828</v>
       </c>
       <c r="F67">
-        <v>0.7290021004839887</v>
+        <v>-0.1484344737877483</v>
       </c>
       <c r="G67">
-        <v>-9.743709462138801</v>
+        <v>-9.292593682751153</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.223438103235738</v>
       </c>
       <c r="E68">
-        <v>-22.18980091389078</v>
+        <v>-21.01876144874212</v>
       </c>
       <c r="F68">
-        <v>-0.3091650860551448</v>
+        <v>-0.2992337892629816</v>
       </c>
       <c r="G68">
-        <v>-8.898718478523666</v>
+        <v>-9.525647020166064</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.063883215559947</v>
       </c>
       <c r="E69">
-        <v>-21.1125160411888</v>
+        <v>-21.20507450877393</v>
       </c>
       <c r="F69">
-        <v>0.1386113986303363</v>
+        <v>-0.3219981538593148</v>
       </c>
       <c r="G69">
-        <v>-9.296692551759202</v>
+        <v>-9.535342020205162</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.879533948751223</v>
       </c>
       <c r="E70">
-        <v>-22.81852235066597</v>
+        <v>-21.5212377208765</v>
       </c>
       <c r="F70">
-        <v>0.2074048263306269</v>
+        <v>-0.2967354331761383</v>
       </c>
       <c r="G70">
-        <v>-9.890674802034045</v>
+        <v>-9.227295044410523</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.669770593971897</v>
       </c>
       <c r="E71">
-        <v>-21.94010154261944</v>
+        <v>-21.22311605876899</v>
       </c>
       <c r="F71">
-        <v>0.4560376455460929</v>
+        <v>-0.4695030521736143</v>
       </c>
       <c r="G71">
-        <v>-9.797099189027067</v>
+        <v>-9.237599653311648</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.44331478840822</v>
       </c>
       <c r="E72">
-        <v>-22.5755428753182</v>
+        <v>-20.84972990103293</v>
       </c>
       <c r="F72">
-        <v>0.05275940100419556</v>
+        <v>-0.578335618288219</v>
       </c>
       <c r="G72">
-        <v>-9.202562155526612</v>
+        <v>-9.446203367630781</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.203725820477693</v>
       </c>
       <c r="E73">
-        <v>-22.73397542772644</v>
+        <v>-21.26472292982112</v>
       </c>
       <c r="F73">
-        <v>-0.2310119350706227</v>
+        <v>-0.5482410305445129</v>
       </c>
       <c r="G73">
-        <v>-8.206583979973622</v>
+        <v>-9.141340194865005</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.956181511687672</v>
       </c>
       <c r="E74">
-        <v>-22.68139992556543</v>
+        <v>-21.36909728362539</v>
       </c>
       <c r="F74">
-        <v>-0.1835597367686558</v>
+        <v>-0.8443740933713082</v>
       </c>
       <c r="G74">
-        <v>-8.631143265380464</v>
+        <v>-9.316722184262222</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.708304287731208</v>
       </c>
       <c r="E75">
-        <v>-22.40751225153829</v>
+        <v>-20.70385665967097</v>
       </c>
       <c r="F75">
-        <v>0.1098364001592899</v>
+        <v>-0.7354371529639508</v>
       </c>
       <c r="G75">
-        <v>-9.028391551619672</v>
+        <v>-8.881320476568487</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.461354656491348</v>
       </c>
       <c r="E76">
-        <v>-24.2326077425436</v>
+        <v>-21.90675956210371</v>
       </c>
       <c r="F76">
-        <v>-0.7111287115287993</v>
+        <v>-0.7322487668305755</v>
       </c>
       <c r="G76">
-        <v>-9.71955224243723</v>
+        <v>-8.972819242253234</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.223035809566763</v>
       </c>
       <c r="E77">
-        <v>-22.63305239253311</v>
+        <v>-21.7241594729963</v>
       </c>
       <c r="F77">
-        <v>-0.710163663504538</v>
+        <v>-0.7308670500027059</v>
       </c>
       <c r="G77">
-        <v>-9.424373626732187</v>
+        <v>-8.813206150186341</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.995147395973375</v>
       </c>
       <c r="E78">
-        <v>-24.60620986726855</v>
+        <v>-22.31406499672965</v>
       </c>
       <c r="F78">
-        <v>-0.1754632737736934</v>
+        <v>-1.148494274695896</v>
       </c>
       <c r="G78">
-        <v>-8.606398628145893</v>
+        <v>-8.34723523407526</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.779378350090738</v>
       </c>
       <c r="E79">
-        <v>-24.78028756673741</v>
+        <v>-22.95710670615285</v>
       </c>
       <c r="F79">
-        <v>-0.2874999650023266</v>
+        <v>-0.928184993716951</v>
       </c>
       <c r="G79">
-        <v>-8.294769710772247</v>
+        <v>-8.830145966465778</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.578711594592918</v>
       </c>
       <c r="E80">
-        <v>-23.26068153472987</v>
+        <v>-23.38870012060638</v>
       </c>
       <c r="F80">
-        <v>-1.153579622181683</v>
+        <v>-1.073697668427518</v>
       </c>
       <c r="G80">
-        <v>-7.357039857791586</v>
+        <v>-7.931800501014358</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.390382519547593</v>
       </c>
       <c r="E81">
-        <v>-24.37489676253222</v>
+        <v>-23.22750983587846</v>
       </c>
       <c r="F81">
-        <v>-0.6928632102970702</v>
+        <v>-1.088717626175078</v>
       </c>
       <c r="G81">
-        <v>-8.717919194099888</v>
+        <v>-7.941666504824175</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.217221201290414</v>
       </c>
       <c r="E82">
-        <v>-24.81767892829484</v>
+        <v>-24.02850232519622</v>
       </c>
       <c r="F82">
-        <v>-1.326556818132067</v>
+        <v>-1.027666120221352</v>
       </c>
       <c r="G82">
-        <v>-8.123131529118686</v>
+        <v>-7.305284457017356</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.058901097291192</v>
       </c>
       <c r="E83">
-        <v>-25.48833533981683</v>
+        <v>-24.31896546562075</v>
       </c>
       <c r="F83">
-        <v>-0.4563808841458674</v>
+        <v>-1.416758572990308</v>
       </c>
       <c r="G83">
-        <v>-7.510729170381243</v>
+        <v>-7.523015334427021</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.9158852237244828</v>
       </c>
       <c r="E84">
-        <v>-25.10896855777301</v>
+        <v>-25.14731931114648</v>
       </c>
       <c r="F84">
-        <v>-1.14040858047717</v>
+        <v>-1.224482073289501</v>
       </c>
       <c r="G84">
-        <v>-7.657416465977533</v>
+        <v>-7.383220404551269</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.7923135003075814</v>
       </c>
       <c r="E85">
-        <v>-26.49889471937411</v>
+        <v>-26.04792657409025</v>
       </c>
       <c r="F85">
-        <v>-0.6006352687715817</v>
+        <v>-1.251783406150967</v>
       </c>
       <c r="G85">
-        <v>-7.754798544598355</v>
+        <v>-7.176130922094981</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.6888192847757533</v>
       </c>
       <c r="E86">
-        <v>-28.28280489027675</v>
+        <v>-27.10042923481697</v>
       </c>
       <c r="F86">
-        <v>-1.11012346823082</v>
+        <v>-1.468365033817314</v>
       </c>
       <c r="G86">
-        <v>-7.879186165269652</v>
+        <v>-6.82835102436819</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6102965846759839</v>
       </c>
       <c r="E87">
-        <v>-28.29835659008257</v>
+        <v>-27.65734580099721</v>
       </c>
       <c r="F87">
-        <v>-1.132851384661431</v>
+        <v>-1.479615919882137</v>
       </c>
       <c r="G87">
-        <v>-7.778112493796996</v>
+        <v>-6.891217754122198</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.5609336716521482</v>
       </c>
       <c r="E88">
-        <v>-29.79241206601977</v>
+        <v>-28.89348270045123</v>
       </c>
       <c r="F88">
-        <v>-1.317697428759126</v>
+        <v>-1.589608200360661</v>
       </c>
       <c r="G88">
-        <v>-8.040930930295188</v>
+        <v>-7.004317820553816</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.5427929217803312</v>
       </c>
       <c r="E89">
-        <v>-30.18590184317366</v>
+        <v>-29.81895316299108</v>
       </c>
       <c r="F89">
-        <v>-0.7114940215534339</v>
+        <v>-1.768449409155463</v>
       </c>
       <c r="G89">
-        <v>-7.875707348101993</v>
+        <v>-6.761946735693223</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.5619574083490509</v>
       </c>
       <c r="E90">
-        <v>-31.44596331646435</v>
+        <v>-31.09965194335485</v>
       </c>
       <c r="F90">
-        <v>-1.509841389675485</v>
+        <v>-1.894381135198655</v>
       </c>
       <c r="G90">
-        <v>-7.173561949417326</v>
+        <v>-6.553846895080174</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.6192666621591872</v>
       </c>
       <c r="E91">
-        <v>-34.00309345255562</v>
+        <v>-32.16943403979852</v>
       </c>
       <c r="F91">
-        <v>-1.507995787102048</v>
+        <v>-1.75364482693263</v>
       </c>
       <c r="G91">
-        <v>-7.371688745692322</v>
+        <v>-6.76367504861254</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.7165281864338298</v>
       </c>
       <c r="E92">
-        <v>-34.04888053080619</v>
+        <v>-33.3607266399727</v>
       </c>
       <c r="F92">
-        <v>-1.139415367961214</v>
+        <v>-2.013695034060882</v>
       </c>
       <c r="G92">
-        <v>-7.6991139732145</v>
+        <v>-6.487938647877519</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.8560345114274963</v>
       </c>
       <c r="E93">
-        <v>-34.78862145950539</v>
+        <v>-34.73134867533599</v>
       </c>
       <c r="F93">
-        <v>-1.002337958513354</v>
+        <v>-1.908281140217631</v>
       </c>
       <c r="G93">
-        <v>-7.446191564088922</v>
+        <v>-7.072199790667352</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.034269393945024</v>
       </c>
       <c r="E94">
-        <v>-37.02359737615802</v>
+        <v>-36.11208378027524</v>
       </c>
       <c r="F94">
-        <v>-0.7856420161454205</v>
+        <v>-2.036759267657029</v>
       </c>
       <c r="G94">
-        <v>-7.477134108982797</v>
+        <v>-6.846088423120213</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.251887333411632</v>
       </c>
       <c r="E95">
-        <v>-38.26042163208629</v>
+        <v>-38.61102950231133</v>
       </c>
       <c r="F95">
-        <v>-1.56242366730299</v>
+        <v>-2.415248617670151</v>
       </c>
       <c r="G95">
-        <v>-7.707453996810811</v>
+        <v>-7.125769658932406</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.506631308653286</v>
       </c>
       <c r="E96">
-        <v>-42.78060032654837</v>
+        <v>-39.49289955236313</v>
       </c>
       <c r="F96">
-        <v>-2.161038400731635</v>
+        <v>-2.305829567434364</v>
       </c>
       <c r="G96">
-        <v>-8.478371629514584</v>
+        <v>-7.541611668149521</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.789522758082606</v>
       </c>
       <c r="E97">
-        <v>-42.57668595692194</v>
+        <v>-41.74740179205945</v>
       </c>
       <c r="F97">
-        <v>-2.077314478963287</v>
+        <v>-2.41706522738449</v>
       </c>
       <c r="G97">
-        <v>-7.767063822687405</v>
+        <v>-7.731395830083615</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.101266537612442</v>
       </c>
       <c r="E98">
-        <v>-43.47502141327103</v>
+        <v>-43.28302053032987</v>
       </c>
       <c r="F98">
-        <v>-2.097469486240802</v>
+        <v>-2.524415844215486</v>
       </c>
       <c r="G98">
-        <v>-8.364663259593236</v>
+        <v>-7.931419332304055</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.419745816425484</v>
       </c>
       <c r="E99">
-        <v>-45.40233574140301</v>
+        <v>-44.96716848860446</v>
       </c>
       <c r="F99">
-        <v>-2.762171371064792</v>
+        <v>-2.586403405334376</v>
       </c>
       <c r="G99">
-        <v>-8.627634424650008</v>
+        <v>-8.219278725547911</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.749307863297107</v>
       </c>
       <c r="E100">
-        <v>-48.63694601522297</v>
+        <v>-46.61435078948243</v>
       </c>
       <c r="F100">
-        <v>-2.402410579661564</v>
+        <v>-2.864029912015228</v>
       </c>
       <c r="G100">
-        <v>-8.612392897727089</v>
+        <v>-8.35965324072289</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.051630357791189</v>
       </c>
       <c r="E101">
-        <v>-49.03115222133039</v>
+        <v>-48.54558886401355</v>
       </c>
       <c r="F101">
-        <v>-2.421955080163216</v>
+        <v>-2.892125649215978</v>
       </c>
       <c r="G101">
-        <v>-8.993595547709313</v>
+        <v>-8.630908298367265</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.35015170643687</v>
       </c>
       <c r="E102">
-        <v>-50.9413657018324</v>
+        <v>-50.76242770681065</v>
       </c>
       <c r="F102">
-        <v>-2.122713154473714</v>
+        <v>-3.047267266616687</v>
       </c>
       <c r="G102">
-        <v>-8.457236346677226</v>
+        <v>-8.644647341777999</v>
       </c>
     </row>
   </sheetData>
